--- a/money-leak-finder/money-leak-finder-sample.xlsx
+++ b/money-leak-finder/money-leak-finder-sample.xlsx
@@ -943,7 +943,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  sample data throughout</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  sample data throughout</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  sample data throughout</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  sample data throughout</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Built by Automated Workflow LLC  ·  automatedworkflowllc.com  ·  sample data throughout</t>
+          <t>Built by Automated Workflow  ·  automatedworkflowllc.com  ·  sample data throughout</t>
         </is>
       </c>
     </row>
